--- a/analysis/econometrics_outputs/contdid/Graficos/unemployment/contdid_cosine_nearest_continuous.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/unemployment/contdid_cosine_nearest_continuous.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">Pre</t>
   </si>
   <si>
-    <t xml:space="preserve">Post</t>
+    <t xml:space="preserve">*</t>
   </si>
   <si>
-    <t xml:space="preserve">*</t>
+    <t xml:space="preserve">Post</t>
   </si>
 </sst>
 </file>
@@ -406,8 +406,8 @@
     <col min="4" max="4" width="4.24625" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="8.96125" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="7.7825" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="10.14" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="8.96125" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="8.96125" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="7.7825" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="12.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="5.425" hidden="0" customWidth="1"/>
     <col min="11" max="11" width="3.71" hidden="0" customWidth="1"/>
@@ -515,13 +515,13 @@
         <v>0.009</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.0187</v>
+        <v>0.0217</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>-0.7921</v>
+        <v>-0.0622</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>0.81</v>
+        <v>0.0802</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -543,13 +543,13 @@
         <v>-0.0581</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>0.0325</v>
+        <v>0.0291</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>-1.4458</v>
+        <v>-0.1534</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>1.3295</v>
+        <v>0.0372</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -571,13 +571,13 @@
         <v>0.0226</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>0.0197</v>
+        <v>0.0246</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>-0.8181</v>
+        <v>-0.0579</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>0.8634</v>
+        <v>0.1032</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -599,13 +599,13 @@
         <v>-0.0514</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0.0321</v>
+        <v>0.0382</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>-1.423</v>
+        <v>-0.1767</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>1.3202</v>
+        <v>0.0739</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -627,13 +627,13 @@
         <v>0.1168</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0.0627</v>
+        <v>0.0451</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>-2.5631</v>
+        <v>-0.0311</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>2.7966</v>
+        <v>0.2647</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -655,13 +655,13 @@
         <v>0.1304</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>0.0667</v>
+        <v>0.0491</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>-2.7187</v>
+        <v>-0.0306</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>2.9795</v>
+        <v>0.2914</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -683,13 +683,13 @@
         <v>0.1722</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0.0165</v>
+        <v>0.0546</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>-0.5339</v>
+        <v>-0.0069</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>0.8783</v>
+        <v>0.3513</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -711,13 +711,13 @@
         <v>-0.2077</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.0681</v>
+        <v>0.0662</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>-3.1185</v>
+        <v>-0.425</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>2.703</v>
+        <v>0.0095</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -739,13 +739,13 @@
         <v>-0.1215</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.0476</v>
+        <v>0.0644</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>-2.1546</v>
+        <v>-0.3328</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>1.9116</v>
+        <v>0.0897</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -767,16 +767,16 @@
         <v>0.1102</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.0106</v>
+        <v>0.0326</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>-0.3413</v>
+        <v>0.0032</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0.5618</v>
+        <v>0.2172</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>11</v>
@@ -795,13 +795,13 @@
         <v>-0.0763</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.0757</v>
+        <v>0.0435</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>-3.3113</v>
+        <v>-0.219</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>3.1588</v>
+        <v>0.0665</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -823,13 +823,13 @@
         <v>0.0477</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.0173</v>
+        <v>0.041</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>-0.6909</v>
+        <v>-0.0868</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>0.7863</v>
+        <v>0.1822</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -851,13 +851,13 @@
         <v>-0.0699</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.0107</v>
+        <v>0.0391</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>-0.5269</v>
+        <v>-0.1981</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>0.3872</v>
+        <v>0.0584</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -879,13 +879,13 @@
         <v>-0.078</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.0122</v>
+        <v>0.0423</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>-0.5972</v>
+        <v>-0.2167</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>0.4412</v>
+        <v>0.0607</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -907,13 +907,13 @@
         <v>0.0399</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.0362</v>
+        <v>0.0393</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>-1.5085</v>
+        <v>-0.0891</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>1.5882</v>
+        <v>0.1689</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -935,13 +935,13 @@
         <v>-0.0639</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.0554</v>
+        <v>0.0383</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>-2.429</v>
+        <v>-0.1896</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>2.3011</v>
+        <v>0.0617</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -963,13 +963,13 @@
         <v>-0.0681</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.046</v>
+        <v>0.0352</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>-2.0354</v>
+        <v>-0.1836</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>1.8992</v>
+        <v>0.0474</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -991,16 +991,16 @@
         <v>0.2576</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.027</v>
+        <v>0.0604</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>-0.8959</v>
+        <v>0.0594</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>1.411</v>
+        <v>0.4557</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>11</v>
@@ -1019,16 +1019,16 @@
         <v>0.1547</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.0257</v>
+        <v>0.0434</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>-0.9453</v>
+        <v>0.0123</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>1.2548</v>
+        <v>0.2972</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>11</v>
@@ -1047,19 +1047,19 @@
         <v>-0.1523</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.0248</v>
+        <v>0.0636</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>-1.2139</v>
+        <v>-0.3608</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>0.9092</v>
+        <v>0.0561</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1075,19 +1075,19 @@
         <v>-0.0261</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.0754</v>
+        <v>0.0813</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>-3.2495</v>
+        <v>-0.2927</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>3.1973</v>
+        <v>0.2405</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -1103,19 +1103,19 @@
         <v>-0.0587</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.0812</v>
+        <v>0.0974</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>-3.5303</v>
+        <v>-0.3781</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>3.4128</v>
+        <v>0.2606</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1131,19 +1131,19 @@
         <v>-0.0978</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.0876</v>
+        <v>0.1147</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>-3.8408</v>
+        <v>-0.4739</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>3.6452</v>
+        <v>0.2783</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -1159,19 +1159,19 @@
         <v>-0.1894</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.1066</v>
+        <v>0.1443</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>-4.743</v>
+        <v>-0.6627</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>4.3641</v>
+        <v>0.2839</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -1187,19 +1187,19 @@
         <v>-0.1178</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.1224</v>
+        <v>0.1433</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>-5.3496</v>
+        <v>-0.5879</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>5.114</v>
+        <v>0.3523</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -1215,19 +1215,19 @@
         <v>-0.0731</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.1934</v>
+        <v>0.1478</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>-8.3371</v>
+        <v>-0.5579</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>8.191</v>
+        <v>0.4118</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -1243,19 +1243,19 @@
         <v>-0.024</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>0.1173</v>
+        <v>0.1281</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>-5.0363</v>
+        <v>-0.4442</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>4.9882</v>
+        <v>0.3961</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -1271,19 +1271,19 @@
         <v>-0.0299</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.0521</v>
+        <v>0.1448</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>-2.2563</v>
+        <v>-0.5049</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>2.1966</v>
+        <v>0.4451</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -1299,19 +1299,19 @@
         <v>0.1354</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.023</v>
+        <v>0.1414</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>-0.8457</v>
+        <v>-0.3283</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>1.1166</v>
+        <v>0.5992</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -1327,19 +1327,19 @@
         <v>0.3215</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>0.1325</v>
+        <v>0.0963</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>-5.3409</v>
+        <v>0.0055</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>5.9839</v>
+        <v>0.6375</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -1355,19 +1355,19 @@
         <v>0.2612</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.0745</v>
+        <v>0.114</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>-2.9205</v>
+        <v>-0.1127</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>3.4429</v>
+        <v>0.6352</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -1383,19 +1383,19 @@
         <v>0.2071</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.1162</v>
+        <v>0.1195</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>-4.7595</v>
+        <v>-0.1849</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>5.1736</v>
+        <v>0.599</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -1411,19 +1411,19 @@
         <v>0.1907</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.1295</v>
+        <v>0.1698</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>-5.342</v>
+        <v>-0.366</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>5.7234</v>
+        <v>0.7474</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -1439,19 +1439,19 @@
         <v>0.2889</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.1177</v>
+        <v>0.1573</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>-4.741</v>
+        <v>-0.2268</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>5.3188</v>
+        <v>0.8047</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -1467,19 +1467,19 @@
         <v>0.1621</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.1408</v>
+        <v>0.1288</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>-5.8554</v>
+        <v>-0.2604</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>6.1796</v>
+        <v>0.5846</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -1495,19 +1495,19 @@
         <v>0.2213</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.2008</v>
+        <v>0.1397</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>-8.3594</v>
+        <v>-0.2368</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>8.8019</v>
+        <v>0.6793</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -1523,19 +1523,19 @@
         <v>0.3138</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.0944</v>
+        <v>0.1469</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>-3.721</v>
+        <v>-0.1681</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>4.3485</v>
+        <v>0.7956</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -1551,19 +1551,19 @@
         <v>0.4198</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.2474</v>
+        <v>0.1479</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>-10.1515</v>
+        <v>-0.0654</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>10.9911</v>
+        <v>0.905</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -1579,19 +1579,19 @@
         <v>0.1891</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.1301</v>
+        <v>0.1613</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>-5.3709</v>
+        <v>-0.3398</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>5.749</v>
+        <v>0.7179</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -1607,19 +1607,19 @@
         <v>0.2363</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.1705</v>
+        <v>0.1567</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>-7.0479</v>
+        <v>-0.2778</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>7.5205</v>
+        <v>0.7504</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -1635,19 +1635,19 @@
         <v>0.327</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.096</v>
+        <v>0.1665</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>-3.7763</v>
+        <v>-0.2192</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>4.4302</v>
+        <v>0.8731</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -1663,19 +1663,19 @@
         <v>0.5673</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.0133</v>
+        <v>0.1428</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>0</v>
+        <v>0.0989</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>1.1345</v>
+        <v>1.0356</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -1691,19 +1691,19 @@
         <v>0.7019</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.1198</v>
+        <v>0.1403</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>-4.4151</v>
+        <v>0.2416</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>5.8189</v>
+        <v>1.1622</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -1719,19 +1719,19 @@
         <v>0.4928</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.1719</v>
+        <v>0.1656</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>-6.8517</v>
+        <v>-0.0504</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>7.8373</v>
+        <v>1.036</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -1747,19 +1747,19 @@
         <v>0.5045</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>0.1234</v>
+        <v>0.1718</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>-4.7677</v>
+        <v>-0.0591</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>5.7767</v>
+        <v>1.0681</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -1775,19 +1775,19 @@
         <v>0.4485</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>0.1948</v>
+        <v>0.222</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>-7.8754</v>
+        <v>-0.2797</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>8.7723</v>
+        <v>1.1766</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -1803,19 +1803,19 @@
         <v>0.5461</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>0.0946</v>
+        <v>0.1618</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>-3.4939</v>
+        <v>0.0156</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>4.5861</v>
+        <v>1.0766</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -1831,19 +1831,19 @@
         <v>0.4599</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0.1495</v>
+        <v>0.2073</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>-5.9284</v>
+        <v>-0.2199</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>6.8481</v>
+        <v>1.1396</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -1859,19 +1859,19 @@
         <v>0.7038</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>0.2646</v>
+        <v>0.1695</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>-10.6024</v>
+        <v>0.1478</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>12.01</v>
+        <v>1.2598</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -1887,19 +1887,19 @@
         <v>0.8229</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.1404</v>
+        <v>0.2024</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>-5.1769</v>
+        <v>0.1591</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>6.8227</v>
+        <v>1.4866</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -1915,19 +1915,19 @@
         <v>0.7106</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.0554</v>
+        <v>0.1843</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>-1.6584</v>
+        <v>0.1062</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>3.0795</v>
+        <v>1.3149</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -1943,19 +1943,19 @@
         <v>0.6869</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>0.3555</v>
+        <v>0.1824</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>-14.5031</v>
+        <v>0.0886</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>15.8769</v>
+        <v>1.2851</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -1971,19 +1971,19 @@
         <v>0.6859</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>0.3427</v>
+        <v>0.2162</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>-13.9579</v>
+        <v>-0.0233</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>15.3296</v>
+        <v>1.395</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -1999,19 +1999,19 @@
         <v>0.9085</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>0.0856</v>
+        <v>0.1967</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>-2.7478</v>
+        <v>0.2633</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>4.5648</v>
+        <v>1.5537</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -2027,19 +2027,19 @@
         <v>0.9824</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>0.1372</v>
+        <v>0.2189</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>-4.88</v>
+        <v>0.2646</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>6.8448</v>
+        <v>1.7001</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -2055,19 +2055,19 @@
         <v>1.052</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>0.1781</v>
+        <v>0.187</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>-6.5601</v>
+        <v>0.4386</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>8.6641</v>
+        <v>1.6654</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -2083,19 +2083,19 @@
         <v>0.994</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>0.1013</v>
+        <v>0.2282</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>-3.3336</v>
+        <v>0.2456</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>5.3216</v>
+        <v>1.7424</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -2111,19 +2111,19 @@
         <v>1.0533</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>0.0074</v>
+        <v>0.2394</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>0.7359</v>
+        <v>0.2683</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>1.3707</v>
+        <v>1.8383</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -2139,19 +2139,19 @@
         <v>0.9434</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>0.2008</v>
+        <v>0.1988</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>-7.6374</v>
+        <v>0.2915</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>9.5243</v>
+        <v>1.5954</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -2167,19 +2167,19 @@
         <v>0.9209</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>0.0345</v>
+        <v>0.2493</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>-0.5512</v>
+        <v>0.1034</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>2.3931</v>
+        <v>1.7385</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -2195,19 +2195,19 @@
         <v>0.9813</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>0.114</v>
+        <v>0.2083</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>-3.8909</v>
+        <v>0.2982</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>5.8535</v>
+        <v>1.6644</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -2223,19 +2223,19 @@
         <v>1.0562</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>0.1698</v>
+        <v>0.1832</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>-6.2004</v>
+        <v>0.4554</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>8.3127</v>
+        <v>1.6569</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
